--- a/data/trans_orig/IP25-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP25-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>119084</t>
+          <t>119539</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129972</t>
+          <t>130210</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>129024</t>
+          <t>129232</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>142291</t>
+          <t>141731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>252945</t>
+          <t>253222</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>269216</t>
+          <t>269599</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>7783</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18909</t>
+          <t>18454</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>11346</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24053</t>
+          <t>23845</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21854</t>
+          <t>21471</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38125</t>
+          <t>37848</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164940</t>
+          <t>164458</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>179257</t>
+          <t>178850</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>176621</t>
+          <t>174118</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>191442</t>
+          <t>191305</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>344613</t>
+          <t>344103</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>366275</t>
+          <t>365772</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15906</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30223</t>
+          <t>30705</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20700</t>
+          <t>20837</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35521</t>
+          <t>38024</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41030</t>
+          <t>41533</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62692</t>
+          <t>63202</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116416</t>
+          <t>116227</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127228</t>
+          <t>127562</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124876</t>
+          <t>124654</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137519</t>
+          <t>137625</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>245222</t>
+          <t>244577</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>261599</t>
+          <t>261746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21401</t>
+          <t>21590</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12138</t>
+          <t>12032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24781</t>
+          <t>25003</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25875</t>
+          <t>25728</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42252</t>
+          <t>42897</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>186281</t>
+          <t>186389</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>198566</t>
+          <t>198997</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>170377</t>
+          <t>170765</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>186912</t>
+          <t>187003</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>362594</t>
+          <t>362518</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>383636</t>
+          <t>382593</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10038</t>
+          <t>9607</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22323</t>
+          <t>22215</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20912</t>
+          <t>20821</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37447</t>
+          <t>37059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32792</t>
+          <t>33835</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53834</t>
+          <t>53910</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>601092</t>
+          <t>600298</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>625225</t>
+          <t>625132</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>616993</t>
+          <t>616543</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>645702</t>
+          <t>645662</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1227233</t>
+          <t>1227346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1264402</t>
+          <t>1263383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54352</t>
+          <t>54445</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78485</t>
+          <t>79279</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76998</t>
+          <t>77038</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>105707</t>
+          <t>106157</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>137875</t>
+          <t>138894</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>175044</t>
+          <t>174931</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123120</t>
+          <t>122370</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>132779</t>
+          <t>132910</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>134522</t>
+          <t>135816</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146591</t>
+          <t>146802</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>261656</t>
+          <t>260517</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>277590</t>
+          <t>276815</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>16046</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20162</t>
+          <t>18868</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15510</t>
+          <t>16285</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>32583</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>179956</t>
+          <t>179527</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>192781</t>
+          <t>192390</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>193573</t>
+          <t>192493</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>207823</t>
+          <t>207603</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>376329</t>
+          <t>377132</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>396915</t>
+          <t>397167</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>13968</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26402</t>
+          <t>26831</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14718</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28968</t>
+          <t>30048</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31984</t>
+          <t>31732</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>52570</t>
+          <t>51767</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122883</t>
+          <t>123595</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>137865</t>
+          <t>137958</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>143025</t>
+          <t>143380</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155598</t>
+          <t>155503</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>270675</t>
+          <t>271293</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>289790</t>
+          <t>289547</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17511</t>
+          <t>17418</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32493</t>
+          <t>31781</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>22227</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31193</t>
+          <t>31436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50308</t>
+          <t>49690</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>177803</t>
+          <t>178378</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>193027</t>
+          <t>193619</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>185155</t>
+          <t>183475</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>197289</t>
+          <t>197006</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>367757</t>
+          <t>366870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>388251</t>
+          <t>387420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17273</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>31922</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>24174</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29698</t>
+          <t>30529</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50192</t>
+          <t>51079</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>617612</t>
+          <t>618615</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>645912</t>
+          <t>646696</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>672442</t>
+          <t>670650</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>697686</t>
+          <t>697623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1299481</t>
+          <t>1298862</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1335811</t>
+          <t>1337184</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64538</t>
+          <t>63754</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92838</t>
+          <t>91835</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52796</t>
+          <t>52859</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78040</t>
+          <t>79832</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>125120</t>
+          <t>123747</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>161450</t>
+          <t>162069</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112834</t>
+          <t>113169</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>124683</t>
+          <t>124626</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128046</t>
+          <t>128162</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140358</t>
+          <t>140342</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>245999</t>
+          <t>245820</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>263013</t>
+          <t>261995</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20873</t>
+          <t>20538</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20030</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18770</t>
+          <t>19788</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35784</t>
+          <t>35963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>180287</t>
+          <t>180380</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>193346</t>
+          <t>192711</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>196939</t>
+          <t>196274</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>210659</t>
+          <t>210480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>381812</t>
+          <t>381241</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>400834</t>
+          <t>399924</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13901</t>
+          <t>14536</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26960</t>
+          <t>26867</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13700</t>
+          <t>13879</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27420</t>
+          <t>28085</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30772</t>
+          <t>31682</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49794</t>
+          <t>50365</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>140260</t>
+          <t>139873</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149391</t>
+          <t>149548</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>152571</t>
+          <t>152064</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>161821</t>
+          <t>161949</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>296083</t>
+          <t>297059</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>309687</t>
+          <t>309879</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>16124</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>14609</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12983</t>
+          <t>12791</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26587</t>
+          <t>25611</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171116</t>
+          <t>171884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187404</t>
+          <t>188163</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>173919</t>
+          <t>173048</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>188295</t>
+          <t>188385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>350533</t>
+          <t>350627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>372701</t>
+          <t>372030</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,05%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>19257</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36304</t>
+          <t>35536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17441</t>
+          <t>17351</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31817</t>
+          <t>32688</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>40455</t>
+          <t>41126</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62623</t>
+          <t>62529</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>618103</t>
+          <t>618652</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>644853</t>
+          <t>644628</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>666379</t>
+          <t>666188</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>691435</t>
+          <t>691607</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1292026</t>
+          <t>1294340</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1329840</t>
+          <t>1330065</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59518</t>
+          <t>59743</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86268</t>
+          <t>85719</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53409</t>
+          <t>53237</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78465</t>
+          <t>78656</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>119375</t>
+          <t>119150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>157189</t>
+          <t>154875</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
